--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.99897579807105</v>
+        <v>5.524833567186546</v>
       </c>
       <c r="D2" t="n">
-        <v>33.38940271293367</v>
+        <v>5.425777940851722</v>
       </c>
       <c r="E2" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F2" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.38843680361293</v>
+        <v>8.025620980587101</v>
       </c>
       <c r="D3" t="n">
-        <v>50.08698484004837</v>
+        <v>8.139135036507859</v>
       </c>
       <c r="E3" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F3" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.73701377735457</v>
+        <v>1.907264738820118</v>
       </c>
       <c r="D4" t="n">
-        <v>11.17212271055441</v>
+        <v>1.815469940465092</v>
       </c>
       <c r="E4" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F4" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.82995005263694</v>
+        <v>7.447366883553503</v>
       </c>
       <c r="D5" t="n">
-        <v>45.72691488787536</v>
+        <v>7.430623669279746</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F5" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.09159254291409</v>
+        <v>5.864883788223541</v>
       </c>
       <c r="D6" t="n">
-        <v>35.49904978513207</v>
+        <v>5.768595590083962</v>
       </c>
       <c r="E6" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F6" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.27987999233466</v>
+        <v>6.707980498754383</v>
       </c>
       <c r="D7" t="n">
-        <v>42.04927223662662</v>
+        <v>6.833006738451826</v>
       </c>
       <c r="E7" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F7" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.5084819573395</v>
+        <v>3.170128318067669</v>
       </c>
       <c r="D8" t="n">
-        <v>18.33350855194994</v>
+        <v>2.979195139691865</v>
       </c>
       <c r="E8" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F8" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.96543145309042</v>
+        <v>6.494382611127194</v>
       </c>
       <c r="D9" t="n">
-        <v>39.17184386945986</v>
+        <v>6.365424628787227</v>
       </c>
       <c r="E9" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F9" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32674054852062</v>
+        <v>4.603095339134601</v>
       </c>
       <c r="D10" t="n">
-        <v>27.20845169325114</v>
+        <v>4.42137340015331</v>
       </c>
       <c r="E10" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F10" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.19262351284154</v>
+        <v>4.74380132083675</v>
       </c>
       <c r="D11" t="n">
-        <v>28.40758892305789</v>
+        <v>4.616233199996908</v>
       </c>
       <c r="E11" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F11" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.62149492651542</v>
+        <v>3.838492925558755</v>
       </c>
       <c r="D12" t="n">
-        <v>22.88555550411577</v>
+        <v>3.718902769418813</v>
       </c>
       <c r="E12" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F12" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.92072779997836</v>
+        <v>3.237118267496483</v>
       </c>
       <c r="D13" t="n">
-        <v>19.11450174224043</v>
+        <v>3.10610653311407</v>
       </c>
       <c r="E13" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F13" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.03892328092718</v>
+        <v>2.931325033150667</v>
       </c>
       <c r="D14" t="n">
-        <v>17.28399043892404</v>
+        <v>2.808648446325156</v>
       </c>
       <c r="E14" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F14" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.85523554301989</v>
+        <v>3.226475775740732</v>
       </c>
       <c r="D15" t="n">
-        <v>19.32487582107352</v>
+        <v>3.140292320924446</v>
       </c>
       <c r="E15" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F15" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.36616860545764</v>
+        <v>7.534502398386866</v>
       </c>
       <c r="D16" t="n">
-        <v>45.74395994562465</v>
+        <v>7.433393491164006</v>
       </c>
       <c r="E16" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F16" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>43.46601397782709</v>
+        <v>7.063227271396902</v>
       </c>
       <c r="D17" t="n">
-        <v>43.21346910343406</v>
+        <v>7.022188729308034</v>
       </c>
       <c r="E17" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F17" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13.10021798218824</v>
+        <v>2.128785422105589</v>
       </c>
       <c r="D18" t="n">
-        <v>12.55425799979785</v>
+        <v>2.040066924967151</v>
       </c>
       <c r="E18" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F18" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>66.76297753159595</v>
+        <v>10.84898384888434</v>
       </c>
       <c r="D19" t="n">
-        <v>65.94760340927432</v>
+        <v>10.71648555400708</v>
       </c>
       <c r="E19" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F19" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>22.395537097063</v>
+        <v>3.639274778272737</v>
       </c>
       <c r="D20" t="n">
-        <v>22.87844326668975</v>
+        <v>3.717747030837084</v>
       </c>
       <c r="E20" t="n">
-        <v>14.15361803263871</v>
+        <v>2.29996293030379</v>
       </c>
       <c r="F20" t="n">
-        <v>14.30857923638167</v>
+        <v>2.325144125912022</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
